--- a/docs/evidence/20261025_NonNV_Cerebras_OpenAI/NonNV_Cerebras_OpenAI.xlsx
+++ b/docs/evidence/20261025_NonNV_Cerebras_OpenAI/NonNV_Cerebras_OpenAI.xlsx
@@ -25314,6 +25314,253 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">資本支出，只作下界）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(c) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反向：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">half the cost of a GPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」若指 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每顆（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$8.4M÷72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的一半、每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k≈1.48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、持有比≈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；若指 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每顆（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4.3M÷72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的一半 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k≈0.76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、持有比≈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（口徑不明，只作交叉檢核）。</t>
     </r>
   </si>
   <si>
@@ -30616,7 +30863,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="111.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
         <v>581</v>
       </c>

--- a/docs/evidence/20261025_NonNV_Cerebras_OpenAI/NonNV_Cerebras_OpenAI.xlsx
+++ b/docs/evidence/20261025_NonNV_Cerebras_OpenAI/NonNV_Cerebras_OpenAI.xlsx
@@ -30027,26 +30027,64 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k≈1.48</t>
+      <t xml:space="preserve">2.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">r1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：每顆所攤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.26 kW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）→ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k≈1.25</t>
     </r>
     <r>
       <rPr>
@@ -30065,7 +30103,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.37</t>
+      <t xml:space="preserve">1.20</t>
     </r>
     <r>
       <rPr>
@@ -30122,7 +30160,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">k≈0.76</t>
+      <t xml:space="preserve">k≈0.64</t>
     </r>
     <r>
       <rPr>
@@ -30141,7 +30179,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.81</t>
+      <t xml:space="preserve">0.72</t>
     </r>
     <r>
       <rPr>
